--- a/Result/profitability/6101.xlsx
+++ b/Result/profitability/6101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02499999999999995</v>
+        <v>0.04125000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>6.48875</v>
+        <v>8.465</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09374999999999994</v>
+        <v>-0.04499999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>7.26375</v>
+        <v>8.3125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1399999999999999</v>
+        <v>-0.10125</v>
       </c>
       <c r="N4" t="n">
-        <v>7.233750000000001</v>
+        <v>5.65375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2399999999999999</v>
+        <v>-0.1562499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2475</v>
+        <v>4.6175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2649999999999999</v>
+        <v>-0.2199999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24625</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.52</v>
+        <v>-0.495</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.848750000000001</v>
+        <v>-9.46875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6124999999999999</v>
+        <v>-0.68375</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.85</v>
+        <v>-13.42</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.31</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8674999999999999</v>
+        <v>-0.8674999999999998</v>
       </c>
       <c r="N10" t="n">
         <v>-16.475</v>
@@ -2026,7 +2026,7 @@
         <v>-0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6575</v>
+        <v>-0.6574999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-15.25</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>369</v>
+      </c>
+      <c r="D75" t="n">
+        <v>341</v>
+      </c>
+      <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>39</v>
+      </c>
+      <c r="K75" t="n">
+        <v>39</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.10375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.181249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6263736263736264</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6242544731610338</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.03030303030303</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6434782608695653</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
